--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1100,6 +1100,9 @@
     <t>Allows an appropriate address to be chosen from a list of many.</t>
   </si>
   <si>
+    <t>billing</t>
+  </si>
+  <si>
     <t>home</t>
   </si>
   <si>
@@ -1110,6 +1113,9 @@
   </si>
   <si>
     <t>Address.use</t>
+  </si>
+  <si>
+    <t>1826-1: fixed value = #billing</t>
   </si>
   <si>
     <t>XAD.7</t>
@@ -6670,7 +6676,7 @@
         <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>92</v>
@@ -6701,10 +6707,10 @@
         <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>83</v>
+        <v>347</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>83</v>
@@ -6719,10 +6725,10 @@
         <v>191</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6740,7 +6746,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6755,7 +6761,7 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>83</v>
+        <v>352</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
@@ -6770,7 +6776,7 @@
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -6778,10 +6784,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6807,13 +6813,13 @@
         <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6827,7 +6833,7 @@
         <v>83</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>83</v>
@@ -6842,10 +6848,10 @@
         <v>191</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6863,7 +6869,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6893,7 +6899,7 @@
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>83</v>
@@ -6901,10 +6907,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6930,16 +6936,16 @@
         <v>260</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6952,7 +6958,7 @@
         <v>83</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>83</v>
@@ -6988,7 +6994,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7009,7 +7015,7 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>83</v>
@@ -7018,7 +7024,7 @@
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7026,10 +7032,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7055,10 +7061,10 @@
         <v>260</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7073,7 +7079,7 @@
         <v>83</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>83</v>
@@ -7109,7 +7115,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7124,13 +7130,13 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>83</v>
@@ -7139,7 +7145,7 @@
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -7147,14 +7153,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7176,10 +7182,10 @@
         <v>260</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7194,7 +7200,7 @@
         <v>83</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>83</v>
@@ -7230,7 +7236,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7245,13 +7251,13 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>83</v>
@@ -7260,7 +7266,7 @@
         <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>83</v>
@@ -7268,14 +7274,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7297,13 +7303,13 @@
         <v>260</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7317,7 +7323,7 @@
         <v>83</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>83</v>
@@ -7353,7 +7359,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7374,7 +7380,7 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
@@ -7383,7 +7389,7 @@
         <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>83</v>
@@ -7391,14 +7397,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7420,10 +7426,10 @@
         <v>260</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7474,7 +7480,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7489,13 +7495,13 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>83</v>
@@ -7504,7 +7510,7 @@
         <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>83</v>
@@ -7512,14 +7518,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7541,10 +7547,10 @@
         <v>260</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7559,7 +7565,7 @@
         <v>83</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>83</v>
@@ -7595,7 +7601,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7610,13 +7616,13 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>83</v>
@@ -7625,7 +7631,7 @@
         <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>83</v>
@@ -7633,10 +7639,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7662,13 +7668,13 @@
         <v>260</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7718,7 +7724,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7733,13 +7739,13 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
@@ -7748,7 +7754,7 @@
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -7756,10 +7762,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7785,14 +7791,14 @@
         <v>330</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7805,7 +7811,7 @@
         <v>83</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>83</v>
@@ -7841,7 +7847,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7871,7 +7877,7 @@
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -7879,10 +7885,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7911,11 +7917,11 @@
         <v>187</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7964,7 +7970,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7994,7 +8000,7 @@
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -8002,10 +8008,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8028,17 +8034,17 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8087,7 +8093,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8096,7 +8102,7 @@
         <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>103</v>
@@ -8108,7 +8114,7 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>165</v>
@@ -8117,7 +8123,7 @@
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8125,10 +8131,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8154,10 +8160,10 @@
         <v>330</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8208,7 +8214,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8229,7 +8235,7 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>165</v>
@@ -8246,10 +8252,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8275,16 +8281,16 @@
         <v>252</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8333,7 +8339,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8354,10 +8360,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8371,10 +8377,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8492,10 +8498,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8615,10 +8621,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8740,10 +8746,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8769,16 +8775,16 @@
         <v>225</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8827,7 +8833,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -8848,16 +8854,16 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8865,10 +8871,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8894,16 +8900,16 @@
         <v>158</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8952,7 +8958,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8973,16 +8979,16 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -8990,14 +8996,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9016,16 +9022,16 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9075,7 +9081,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9096,7 +9102,7 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>165</v>
@@ -9105,7 +9111,7 @@
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9113,10 +9119,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9139,19 +9145,19 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9200,7 +9206,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9221,10 +9227,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9238,10 +9244,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9267,16 +9273,16 @@
         <v>252</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9325,7 +9331,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9346,7 +9352,7 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>165</v>
@@ -9363,10 +9369,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9484,10 +9490,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9607,10 +9613,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9732,10 +9738,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9758,16 +9764,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9817,7 +9823,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>91</v>
@@ -9847,7 +9853,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -9855,10 +9861,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9884,10 +9890,10 @@
         <v>111</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9917,28 +9923,28 @@
         <v>191</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -9959,7 +9965,7 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>165</v>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="510">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,7 +559,11 @@
     <t>Need to be able to track the patient by multiple names. Examples are your official name and a partner name.</t>
   </si>
   <si>
-    <t>1827: source value from ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - DEBTOR (430-9 &gt; 340-.01) case patient</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpp-17-1827:If patient then source value from (430-9 &gt; 340-.01) {null}</t>
+  </si>
+  <si>
+    <t>1827: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - DEBTOR (430-9 &gt; 340-.01) if patient</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.ARDebtorIEN
@@ -991,7 +995,7 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>1825: source value from ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - PHONE NUMBER (430-9 &gt; 340-1.07)</t>
+    <t>1825: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - PHONE NUMBER (430-9 &gt; 340-1.07)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.ARDebtorIEN</t>
@@ -1197,7 +1201,7 @@
     <t>Address.line</t>
   </si>
   <si>
-    <t>1821: source value from ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - STREET ADDRESS #3 (430-9 &gt; 340-1.03)</t>
+    <t>1821: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - STREET ADDRESS #3 (430-9 &gt; 340-1.03)</t>
   </si>
   <si>
     <t>AD.part[parttype = AL]</t>
@@ -1225,7 +1229,7 @@
     <t>Address.city</t>
   </si>
   <si>
-    <t>1822: source value from ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - CITY (430-9 &gt; 340-1.04)</t>
+    <t>1822: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - CITY (430-9 &gt; 340-1.04)</t>
   </si>
   <si>
     <t>AD.part[parttype = CTY]</t>
@@ -1278,7 +1282,7 @@
     <t>Address.state</t>
   </si>
   <si>
-    <t>1823: source value from ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - STATE (430-9 &gt; 340-1.05)</t>
+    <t>1823: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - STATE (430-9 &gt; 340-1.05)</t>
   </si>
   <si>
     <t>AD.part[parttype = STA]</t>
@@ -1306,7 +1310,7 @@
     <t>Address.postalCode</t>
   </si>
   <si>
-    <t>1824: source value from ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - ZIP CODE (430-9 &gt; 340-1.06)</t>
+    <t>1824: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - ZIP CODE (430-9 &gt; 340-1.06)</t>
   </si>
   <si>
     <t>AD.part[parttype = ZIP]</t>
@@ -1330,7 +1334,7 @@
     <t>Address.country</t>
   </si>
   <si>
-    <t>1826: source value from ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - FOREIGN COUNTRY CODE (430-9 &gt; 340-1.08)</t>
+    <t>1826: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - FOREIGN COUNTRY CODE (430-9 &gt; 340-1.08)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.ARDebtorIEN
@@ -1956,7 +1960,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="113.046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="117.140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="131.55859375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="40.8125" customWidth="true" bestFit="true"/>
@@ -3552,25 +3556,25 @@
         <v>83</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>83</v>
@@ -3578,10 +3582,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3604,19 +3608,19 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>83</v>
@@ -3665,7 +3669,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3686,16 +3690,16 @@
         <v>83</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>83</v>
@@ -3703,10 +3707,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3732,16 +3736,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>83</v>
@@ -3766,13 +3770,13 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
@@ -3790,7 +3794,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3811,16 +3815,16 @@
         <v>83</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>83</v>
@@ -3828,10 +3832,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3854,19 +3858,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3915,7 +3919,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3936,27 +3940,27 @@
         <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3979,19 +3983,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -4040,7 +4044,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4061,7 +4065,7 @@
         <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>165</v>
@@ -4070,7 +4074,7 @@
         <v>83</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>83</v>
@@ -4078,10 +4082,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4104,19 +4108,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
@@ -4165,7 +4169,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4186,16 +4190,16 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>83</v>
@@ -4203,10 +4207,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4229,17 +4233,17 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4264,13 +4268,13 @@
         <v>83</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>83</v>
@@ -4288,7 +4292,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4309,16 +4313,16 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>83</v>
@@ -4326,10 +4330,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4352,19 +4356,19 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4413,7 +4417,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4434,7 +4438,7 @@
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>165</v>
@@ -4443,7 +4447,7 @@
         <v>83</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>83</v>
@@ -4451,10 +4455,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4477,19 +4481,19 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
@@ -4538,7 +4542,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4559,7 +4563,7 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>165</v>
@@ -4568,7 +4572,7 @@
         <v>83</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>83</v>
@@ -4576,10 +4580,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4602,19 +4606,19 @@
         <v>83</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -4663,7 +4667,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4675,7 +4679,7 @@
         <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>83</v>
@@ -4684,7 +4688,7 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>165</v>
@@ -4701,10 +4705,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4727,13 +4731,13 @@
         <v>83</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4784,7 +4788,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4822,10 +4826,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4854,7 +4858,7 @@
         <v>138</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>140</v>
@@ -4907,7 +4911,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4945,14 +4949,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4974,10 +4978,10 @@
         <v>137</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>140</v>
@@ -5032,7 +5036,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5070,10 +5074,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5096,17 +5100,17 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5131,13 +5135,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5155,7 +5159,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5176,7 +5180,7 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>165</v>
@@ -5185,7 +5189,7 @@
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5193,10 +5197,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5222,14 +5226,14 @@
         <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5278,7 +5282,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5299,7 +5303,7 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>165</v>
@@ -5308,7 +5312,7 @@
         <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -5316,10 +5320,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5342,19 +5346,19 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5403,7 +5407,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5424,7 +5428,7 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>165</v>
@@ -5433,7 +5437,7 @@
         <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5441,10 +5445,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5467,13 +5471,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5524,7 +5528,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5562,10 +5566,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5594,7 +5598,7 @@
         <v>138</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>140</v>
@@ -5635,19 +5639,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5685,10 +5689,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5714,10 +5718,10 @@
         <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5744,13 +5748,13 @@
         <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>83</v>
@@ -5768,7 +5772,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5777,7 +5781,7 @@
         <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
@@ -5789,7 +5793,7 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>83</v>
@@ -5798,7 +5802,7 @@
         <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -5806,10 +5810,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5832,19 +5836,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5893,7 +5897,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5908,13 +5912,13 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>83</v>
@@ -5923,7 +5927,7 @@
         <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -5931,10 +5935,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5960,16 +5964,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -5994,13 +5998,13 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -6018,7 +6022,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6039,7 +6043,7 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>83</v>
@@ -6048,7 +6052,7 @@
         <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>83</v>
@@ -6056,10 +6060,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6082,16 +6086,16 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6141,7 +6145,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6179,10 +6183,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6205,13 +6209,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6262,7 +6266,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6283,7 +6287,7 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>83</v>
@@ -6300,10 +6304,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6326,17 +6330,17 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6385,7 +6389,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6406,7 +6410,7 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>165</v>
@@ -6415,7 +6419,7 @@
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -6423,10 +6427,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6449,13 +6453,13 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6506,7 +6510,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6544,10 +6548,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6576,7 +6580,7 @@
         <v>138</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>140</v>
@@ -6617,19 +6621,19 @@
         <v>83</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6667,10 +6671,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6696,16 +6700,16 @@
         <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6715,10 +6719,10 @@
         <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>83</v>
@@ -6730,13 +6734,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6754,7 +6758,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6769,13 +6773,13 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>83</v>
@@ -6784,7 +6788,7 @@
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -6792,10 +6796,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6821,13 +6825,13 @@
         <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6841,7 +6845,7 @@
         <v>83</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>83</v>
@@ -6853,13 +6857,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6877,7 +6881,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6898,7 +6902,7 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>83</v>
@@ -6907,7 +6911,7 @@
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>83</v>
@@ -6915,10 +6919,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6941,19 +6945,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6966,7 +6970,7 @@
         <v>83</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>83</v>
@@ -7002,7 +7006,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7023,7 +7027,7 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>83</v>
@@ -7032,7 +7036,7 @@
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7040,10 +7044,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7066,13 +7070,13 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7087,7 +7091,7 @@
         <v>83</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>83</v>
@@ -7123,7 +7127,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7138,13 +7142,13 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>83</v>
@@ -7153,7 +7157,7 @@
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -7161,14 +7165,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7187,13 +7191,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7208,7 +7212,7 @@
         <v>83</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>83</v>
@@ -7244,7 +7248,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7259,13 +7263,13 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>83</v>
@@ -7274,7 +7278,7 @@
         <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>83</v>
@@ -7282,14 +7286,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7308,16 +7312,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7331,7 +7335,7 @@
         <v>83</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>83</v>
@@ -7367,7 +7371,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7388,7 +7392,7 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
@@ -7397,7 +7401,7 @@
         <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>83</v>
@@ -7405,14 +7409,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7431,13 +7435,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7488,7 +7492,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7503,13 +7507,13 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>83</v>
@@ -7518,7 +7522,7 @@
         <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>83</v>
@@ -7526,14 +7530,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7552,13 +7556,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7573,7 +7577,7 @@
         <v>83</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>83</v>
@@ -7609,7 +7613,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7624,13 +7628,13 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>83</v>
@@ -7639,7 +7643,7 @@
         <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>83</v>
@@ -7647,10 +7651,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7673,16 +7677,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7732,7 +7736,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7747,13 +7751,13 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
@@ -7762,7 +7766,7 @@
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -7770,10 +7774,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7796,17 +7800,17 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7819,7 +7823,7 @@
         <v>83</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>83</v>
@@ -7855,7 +7859,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7876,7 +7880,7 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>83</v>
@@ -7885,7 +7889,7 @@
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -7893,10 +7897,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7922,14 +7926,14 @@
         <v>111</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7954,13 +7958,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7978,7 +7982,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7999,7 +8003,7 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>165</v>
@@ -8008,7 +8012,7 @@
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -8016,10 +8020,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8042,17 +8046,17 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8101,7 +8105,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8110,7 +8114,7 @@
         <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>103</v>
@@ -8122,7 +8126,7 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>165</v>
@@ -8131,7 +8135,7 @@
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8139,10 +8143,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8165,13 +8169,13 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8222,7 +8226,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8243,7 +8247,7 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>165</v>
@@ -8260,10 +8264,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8286,19 +8290,19 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8347,7 +8351,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8368,10 +8372,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8385,10 +8389,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8411,13 +8415,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8468,7 +8472,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8506,10 +8510,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8538,7 +8542,7 @@
         <v>138</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>140</v>
@@ -8591,7 +8595,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8629,14 +8633,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8658,10 +8662,10 @@
         <v>137</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>140</v>
@@ -8716,7 +8720,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8754,10 +8758,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8780,19 +8784,19 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8841,7 +8845,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -8862,16 +8866,16 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8879,10 +8883,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8908,16 +8912,16 @@
         <v>158</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8966,7 +8970,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8987,16 +8991,16 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9004,14 +9008,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9030,16 +9034,16 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9089,7 +9093,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9110,7 +9114,7 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>165</v>
@@ -9119,7 +9123,7 @@
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9127,10 +9131,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9153,19 +9157,19 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9214,7 +9218,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9235,10 +9239,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9252,10 +9256,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9278,19 +9282,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9339,7 +9343,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9360,7 +9364,7 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>165</v>
@@ -9377,10 +9381,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9403,13 +9407,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9460,7 +9464,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9498,10 +9502,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9530,7 +9534,7 @@
         <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>140</v>
@@ -9583,7 +9587,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9621,14 +9625,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9650,10 +9654,10 @@
         <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
@@ -9708,7 +9712,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9746,10 +9750,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9772,16 +9776,16 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9831,7 +9835,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>91</v>
@@ -9861,7 +9865,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -9869,10 +9873,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9898,10 +9902,10 @@
         <v>111</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9928,13 +9932,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -9952,7 +9956,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -9973,7 +9977,7 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>165</v>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -560,7 +560,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpp-17-1827:If patient then source value from (430-9 &gt; 340-.01) {null}</t>
+dpp-17-1827:If patient then source value from (430-9 &gt; 340-.01) {true}</t>
   </si>
   <si>
     <t>1827: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - DEBTOR (430-9 &gt; 340-.01) if patient</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="567">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,24 +559,248 @@
     <t>Need to be able to track the patient by multiple names. Examples are your official name and a partner name.</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>.patient.name</t>
+  </si>
+  <si>
+    <t>PID-5, PID-9</t>
+  </si>
+  <si>
+    <t>Patient.name.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Patient.name.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Patient.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>Patient.name.text</t>
+  </si>
+  <si>
+    <t>Text representation of the full name</t>
+  </si>
+  <si>
+    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>HumanName.text</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpp-17-1827:If patient then source value from (430-9 &gt; 340-.01) {true}</t>
-  </si>
-  <si>
-    <t>1827: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - DEBTOR (430-9 &gt; 340-.01) if patient</t>
+dpp-17-1827:If POINTER is PATIENT (#2) then source value from (430-9 &gt; 340-.01) {true}</t>
+  </si>
+  <si>
+    <t>1827: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - DEBTOR (430-9 &gt; 340-.01) if POINTER is PATIENT (#2)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.ARDebtorIEN
 Dim.ARDebtor.InstitutionIEN,Dim.ARDebtor.InsuranceCompanyIEN,Dim.ARDebtor.PatientIEN,Dim.ARDebtor.StaffIEN,Dim.ARDebtor.VendorIEN</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>.patient.name</t>
-  </si>
-  <si>
-    <t>PID-5, PID-9</t>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>implied by XPN.11</t>
+  </si>
+  <si>
+    <t>Patient.name.family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surname
+</t>
+  </si>
+  <si>
+    <t>Family name (often called 'Surname')</t>
+  </si>
+  <si>
+    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
+  </si>
+  <si>
+    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
+  </si>
+  <si>
+    <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpp-17-1827-1:If POINTER is PATIENT (#2) then fixed value LAST {true}</t>
+  </si>
+  <si>
+    <t>1827-1: fixed value = LAST if POINTER is PATIENT (#2)</t>
+  </si>
+  <si>
+    <t>./part[partType = FAM]</t>
+  </si>
+  <si>
+    <t>XPN.1/FN.1</t>
+  </si>
+  <si>
+    <t>Patient.name.given</t>
+  </si>
+  <si>
+    <t>first name
+middle name</t>
+  </si>
+  <si>
+    <t>Given names (not always 'first'). Includes middle names</t>
+  </si>
+  <si>
+    <t>Given name.</t>
+  </si>
+  <si>
+    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
+  </si>
+  <si>
+    <t>HumanName.given</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpp-17-1827-2:If POINTER is PATIENT (#2) then fixed value FIRST &amp; MIDDLE {true}</t>
+  </si>
+  <si>
+    <t>1827-2: fixed value = FIRST &amp; MIDDLE if POINTER is PATIENT (#2)</t>
+  </si>
+  <si>
+    <t>./part[partType = GIV]</t>
+  </si>
+  <si>
+    <t>XPN.2 + XPN.3</t>
+  </si>
+  <si>
+    <t>Patient.name.prefix</t>
+  </si>
+  <si>
+    <t>Parts that come before the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
+  </si>
+  <si>
+    <t>HumanName.prefix</t>
+  </si>
+  <si>
+    <t>./part[partType = PFX]</t>
+  </si>
+  <si>
+    <t>XPN.5</t>
+  </si>
+  <si>
+    <t>Patient.name.suffix</t>
+  </si>
+  <si>
+    <t>Parts that come after the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>HumanName.suffix</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+dpp-17-1827-3:If POINTER is PATIENT (#2) then fixed value SUFFIX {true}</t>
+  </si>
+  <si>
+    <t>1827-3: fixed value = SUFFIX if POINTER is PATIENT (#2)</t>
+  </si>
+  <si>
+    <t>./part[partType = SFX]</t>
+  </si>
+  <si>
+    <t>XPN/4</t>
+  </si>
+  <si>
+    <t>Patient.name.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when name was/is in use</t>
+  </si>
+  <si>
+    <t>Indicates the period of time when this name was valid for the named person.</t>
+  </si>
+  <si>
+    <t>Allows names to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>HumanName.period</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
+  </si>
+  <si>
+    <t>XPN.13 + XPN.14</t>
   </si>
   <si>
     <t>Patient.telecom</t>
@@ -620,9 +844,6 @@
   </si>
   <si>
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>The gender of a person used for administrative purposes.</t>
@@ -840,26 +1061,7 @@
     <t>Patient.contact.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Patient.contact.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Patient.contact.modifierExtension</t>
@@ -939,16 +1141,6 @@
     <t>Patient.contact.telecom.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Patient.contact.telecom.system</t>
   </si>
   <si>
@@ -1031,9 +1223,6 @@
     <t>ContactPoint.use</t>
   </si>
   <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
     <t>XTN.2 - but often indicated by field</t>
   </si>
   <si>
@@ -1059,10 +1248,6 @@
     <t>Patient.contact.telecom.period</t>
   </si>
   <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
     <t>Time period when the contact point was/is in use</t>
   </si>
   <si>
@@ -1072,9 +1257,6 @@
     <t>ContactPoint.period</t>
   </si>
   <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
-  </si>
-  <si>
     <t>Patient.contact.address</t>
   </si>
   <si>
@@ -1171,16 +1353,10 @@
     <t>Can provide both a text representation and parts. Applications updating an address SHALL ensure that  when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
   </si>
   <si>
-    <t>A renderable, unencoded form.</t>
-  </si>
-  <si>
     <t>137 Nowhere Street, Erewhon 9132</t>
   </si>
   <si>
     <t>Address.text</t>
-  </si>
-  <si>
-    <t>./formatted</t>
   </si>
   <si>
     <t>XAD.1 + XAD.2 + XAD.3 + XAD.4 + XAD.5 + XAD.6</t>
@@ -1922,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ65"/>
+  <dimension ref="A1:AQ74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.47265625" customWidth="true" bestFit="true"/>
@@ -1960,7 +2136,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="117.140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="125.31640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="131.55859375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="40.8125" customWidth="true" bestFit="true"/>
@@ -3474,7 +3650,7 @@
         <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>83</v>
@@ -3556,25 +3732,25 @@
         <v>83</v>
       </c>
       <c r="AJ13" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>83</v>
@@ -3582,10 +3758,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3596,7 +3772,7 @@
         <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>83</v>
@@ -3605,23 +3781,19 @@
         <v>83</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>83</v>
       </c>
@@ -3669,19 +3841,19 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>83</v>
@@ -3690,16 +3862,16 @@
         <v>83</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>83</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>83</v>
@@ -3707,21 +3879,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>83</v>
@@ -3730,23 +3902,21 @@
         <v>83</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>83</v>
       </c>
@@ -3770,43 +3940,43 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>193</v>
+        <v>83</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>83</v>
+        <v>184</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>83</v>
@@ -3815,16 +3985,16 @@
         <v>83</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>198</v>
+        <v>83</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>83</v>
@@ -3832,10 +4002,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3852,25 +4022,25 @@
         <v>83</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3895,13 +4065,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>83</v>
+        <v>194</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3919,7 +4089,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3940,27 +4110,27 @@
         <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3974,28 +4144,28 @@
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -4044,7 +4214,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4056,25 +4226,25 @@
         <v>83</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>83</v>
@@ -4082,24 +4252,24 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>83</v>
+        <v>210</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>83</v>
@@ -4108,20 +4278,18 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4169,37 +4337,37 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>223</v>
-      </c>
       <c r="AN18" t="s" s="2">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>83</v>
@@ -4207,44 +4375,44 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4268,13 +4436,13 @@
         <v>83</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>232</v>
+        <v>83</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>83</v>
@@ -4292,37 +4460,37 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AK19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>235</v>
+        <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>83</v>
@@ -4330,10 +4498,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4344,7 +4512,7 @@
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>83</v>
@@ -4353,23 +4521,19 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>238</v>
+        <v>177</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>83</v>
       </c>
@@ -4417,13 +4581,13 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>83</v>
@@ -4438,16 +4602,16 @@
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>83</v>
@@ -4455,10 +4619,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4472,29 +4636,25 @@
         <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>246</v>
+        <v>177</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4542,7 +4702,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4554,25 +4714,25 @@
         <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>239</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>240</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>83</v>
@@ -4580,10 +4740,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4594,7 +4754,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4603,22 +4763,20 @@
         <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -4667,19 +4825,19 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>259</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>83</v>
@@ -4688,16 +4846,16 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>83</v>
@@ -4705,10 +4863,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4719,7 +4877,7 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>83</v>
@@ -4728,19 +4886,23 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
@@ -4788,19 +4950,19 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>83</v>
@@ -4809,16 +4971,16 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>165</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>83</v>
+        <v>259</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>83</v>
@@ -4826,21 +4988,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>83</v>
@@ -4849,21 +5011,23 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>138</v>
+        <v>261</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
@@ -4887,13 +5051,13 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>83</v>
+        <v>265</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4911,37 +5075,37 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>269</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -4949,45 +5113,45 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>270</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>137</v>
+        <v>271</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>140</v>
+        <v>274</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>146</v>
+        <v>275</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5036,19 +5200,19 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>83</v>
@@ -5057,27 +5221,27 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>134</v>
+        <v>276</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>83</v>
+        <v>277</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>83</v>
+        <v>278</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>83</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5088,29 +5252,31 @@
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>227</v>
+        <v>281</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5135,13 +5301,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5159,13 +5325,13 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>83</v>
@@ -5180,7 +5346,7 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>165</v>
@@ -5189,7 +5355,7 @@
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5197,10 +5363,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5211,7 +5377,7 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>83</v>
@@ -5220,20 +5386,22 @@
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>289</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5282,13 +5450,13 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>83</v>
@@ -5303,16 +5471,16 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>165</v>
+        <v>295</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -5320,10 +5488,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5334,7 +5502,7 @@
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>83</v>
@@ -5346,19 +5514,17 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>180</v>
+        <v>298</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>184</v>
+        <v>301</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5383,13 +5549,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>83</v>
+        <v>302</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>83</v>
+        <v>303</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5407,13 +5573,13 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>83</v>
@@ -5428,16 +5594,16 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>185</v>
+        <v>305</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>165</v>
+        <v>306</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5445,10 +5611,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5471,16 +5637,20 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>262</v>
+        <v>309</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>310</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5528,7 +5698,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>265</v>
+        <v>308</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5540,7 +5710,7 @@
         <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>83</v>
@@ -5549,16 +5719,16 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AN29" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -5566,14 +5736,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5592,18 +5762,20 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>137</v>
+        <v>317</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>138</v>
+        <v>318</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
       </c>
@@ -5639,19 +5811,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5663,7 +5835,7 @@
         <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>83</v>
@@ -5672,16 +5844,16 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AN30" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -5689,10 +5861,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5703,7 +5875,7 @@
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>83</v>
@@ -5712,19 +5884,23 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>111</v>
+        <v>325</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5748,13 +5924,13 @@
         <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>193</v>
+        <v>83</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>83</v>
@@ -5772,19 +5948,19 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>330</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
@@ -5793,16 +5969,16 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -5810,10 +5986,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5827,29 +6003,25 @@
         <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>307</v>
+        <v>178</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -5897,7 +6069,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5909,16 +6081,16 @@
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>314</v>
+        <v>165</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>83</v>
@@ -5927,7 +6099,7 @@
         <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -5935,46 +6107,44 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>138</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>182</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5998,13 +6168,13 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>193</v>
+        <v>83</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>321</v>
+        <v>83</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -6022,19 +6192,19 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>323</v>
+        <v>186</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -6043,7 +6213,7 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>83</v>
@@ -6052,7 +6222,7 @@
         <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>83</v>
@@ -6060,44 +6230,46 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>83</v>
+        <v>335</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>327</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6145,19 +6317,19 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6166,7 +6338,7 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>83</v>
@@ -6175,7 +6347,7 @@
         <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6183,10 +6355,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6197,7 +6369,7 @@
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6206,19 +6378,21 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6242,13 +6416,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>83</v>
+        <v>302</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6266,13 +6440,13 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -6287,16 +6461,16 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>134</v>
+        <v>346</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>83</v>
@@ -6304,10 +6478,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6330,17 +6504,17 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>218</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6389,7 +6563,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6410,7 +6584,7 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>165</v>
@@ -6419,7 +6593,7 @@
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -6427,10 +6601,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6441,7 +6615,7 @@
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6453,16 +6627,20 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>263</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6510,19 +6688,19 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>265</v>
+        <v>352</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>83</v>
@@ -6531,16 +6709,16 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AN37" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -6548,21 +6726,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -6574,17 +6752,15 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6621,31 +6797,31 @@
         <v>83</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>268</v>
+        <v>180</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>83</v>
@@ -6671,46 +6847,44 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>346</v>
+        <v>138</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>347</v>
+        <v>182</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6719,10 +6893,10 @@
         <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>350</v>
+        <v>83</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>83</v>
@@ -6734,52 +6908,52 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>193</v>
+        <v>83</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>353</v>
+        <v>83</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>83</v>
+        <v>184</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>186</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>355</v>
+        <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>83</v>
@@ -6788,7 +6962,7 @@
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -6796,10 +6970,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6825,14 +6999,12 @@
         <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6845,7 +7017,7 @@
         <v>83</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>361</v>
+        <v>83</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>83</v>
@@ -6857,7 +7029,7 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y40" t="s" s="2">
         <v>362</v>
@@ -6890,7 +7062,7 @@
         <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>83</v>
+        <v>365</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>103</v>
@@ -6902,7 +7074,7 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>324</v>
+        <v>366</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>83</v>
@@ -6911,7 +7083,7 @@
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>83</v>
@@ -6919,10 +7091,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6936,7 +7108,7 @@
         <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>83</v>
@@ -6945,19 +7117,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6970,7 +7142,7 @@
         <v>83</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>83</v>
@@ -7006,7 +7178,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7021,13 +7193,13 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>83</v>
@@ -7036,7 +7208,7 @@
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7044,10 +7216,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7058,28 +7230,32 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>262</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -7091,7 +7267,7 @@
         <v>83</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>83</v>
@@ -7103,13 +7279,13 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>83</v>
+        <v>384</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
@@ -7127,13 +7303,13 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
@@ -7142,13 +7318,13 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>381</v>
+        <v>196</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>83</v>
@@ -7157,7 +7333,7 @@
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -7165,14 +7341,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>384</v>
+        <v>83</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7182,7 +7358,7 @@
         <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>83</v>
@@ -7191,15 +7367,17 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>262</v>
+        <v>388</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7212,7 +7390,7 @@
         <v>83</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>387</v>
+        <v>83</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>83</v>
@@ -7248,7 +7426,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7263,13 +7441,13 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>165</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>83</v>
@@ -7278,7 +7456,7 @@
         <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>391</v>
+        <v>165</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>83</v>
@@ -7286,14 +7464,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7312,7 +7490,7 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>394</v>
@@ -7320,9 +7498,7 @@
       <c r="M44" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>396</v>
-      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7335,7 +7511,7 @@
         <v>83</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>397</v>
+        <v>83</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>83</v>
@@ -7371,7 +7547,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7392,7 +7568,7 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>249</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
@@ -7401,7 +7577,7 @@
         <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>400</v>
+        <v>134</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>83</v>
@@ -7409,14 +7585,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7426,25 +7602,27 @@
         <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7492,7 +7670,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7507,22 +7685,22 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>406</v>
+        <v>83</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>407</v>
+        <v>294</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>83</v>
@@ -7530,14 +7708,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7547,22 +7725,22 @@
         <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>411</v>
+        <v>178</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>412</v>
+        <v>179</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7577,7 +7755,7 @@
         <v>83</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>413</v>
+        <v>83</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>83</v>
@@ -7613,7 +7791,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>414</v>
+        <v>180</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7625,16 +7803,16 @@
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>416</v>
+        <v>165</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>83</v>
@@ -7643,7 +7821,7 @@
         <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>417</v>
+        <v>83</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>83</v>
@@ -7651,42 +7829,42 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>419</v>
+        <v>138</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>420</v>
+        <v>182</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>421</v>
+        <v>140</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7724,40 +7902,40 @@
         <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>83</v>
+        <v>184</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>422</v>
+        <v>186</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>423</v>
+        <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>425</v>
+        <v>165</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
@@ -7766,7 +7944,7 @@
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>426</v>
+        <v>83</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -7774,10 +7952,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>427</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>427</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7791,26 +7969,28 @@
         <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>333</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>428</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7820,10 +8000,10 @@
         <v>83</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>83</v>
@@ -7835,13 +8015,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>411</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>412</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7859,7 +8039,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7874,13 +8054,13 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>83</v>
+        <v>414</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>337</v>
+        <v>196</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>83</v>
@@ -7889,7 +8069,7 @@
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -7897,10 +8077,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7920,21 +8100,21 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>189</v>
+        <v>417</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7946,7 +8126,7 @@
         <v>83</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>83</v>
@@ -7958,13 +8138,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>194</v>
+        <v>421</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>195</v>
+        <v>422</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7982,7 +8162,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8006,13 +8186,13 @@
         <v>196</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -8020,10 +8200,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8043,20 +8223,22 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>439</v>
+        <v>177</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>442</v>
+        <v>202</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8069,7 +8251,7 @@
         <v>83</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>83</v>
+        <v>429</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>83</v>
@@ -8105,7 +8287,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8114,7 +8296,7 @@
         <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>443</v>
+        <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>103</v>
@@ -8126,16 +8308,16 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>444</v>
+        <v>207</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8143,10 +8325,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8157,25 +8339,25 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>333</v>
+        <v>177</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8190,7 +8372,7 @@
         <v>83</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>83</v>
+        <v>435</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>83</v>
@@ -8226,13 +8408,13 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
@@ -8241,22 +8423,22 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>83</v>
+        <v>437</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>83</v>
+        <v>439</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -8264,46 +8446,42 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>83</v>
+        <v>441</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>254</v>
+        <v>177</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8315,7 +8493,7 @@
         <v>83</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>83</v>
+        <v>444</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>83</v>
@@ -8351,13 +8529,13 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
@@ -8366,22 +8544,22 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>83</v>
+        <v>448</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -8389,14 +8567,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8412,18 +8590,20 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>263</v>
+        <v>451</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8436,7 +8616,7 @@
         <v>83</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>83</v>
+        <v>454</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>83</v>
@@ -8472,7 +8652,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>265</v>
+        <v>455</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8484,7 +8664,7 @@
         <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>83</v>
@@ -8493,7 +8673,7 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>165</v>
+        <v>456</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>83</v>
@@ -8502,7 +8682,7 @@
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>83</v>
@@ -8517,36 +8697,34 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>136</v>
+        <v>459</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>138</v>
+        <v>460</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8595,28 +8773,28 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>268</v>
+        <v>462</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>83</v>
+        <v>463</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>165</v>
+        <v>464</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>83</v>
@@ -8625,7 +8803,7 @@
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>83</v>
+        <v>465</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>83</v>
@@ -8633,46 +8811,42 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>270</v>
+        <v>467</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>271</v>
+        <v>468</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8684,7 +8858,7 @@
         <v>83</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>83</v>
@@ -8720,28 +8894,28 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>273</v>
+        <v>471</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>83</v>
+        <v>472</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>134</v>
+        <v>473</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>83</v>
@@ -8750,7 +8924,7 @@
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>83</v>
+        <v>474</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -8758,10 +8932,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8769,35 +8943,33 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8821,13 +8993,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8845,10 +9017,10 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>91</v>
@@ -8860,22 +9032,22 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>83</v>
+        <v>480</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>83</v>
+        <v>481</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -8883,10 +9055,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8906,22 +9078,20 @@
         <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>158</v>
+        <v>244</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8934,7 +9104,7 @@
         <v>83</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>83</v>
+        <v>488</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>83</v>
@@ -8970,7 +9140,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8991,16 +9161,16 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>473</v>
+        <v>249</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>474</v>
+        <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9008,21 +9178,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>477</v>
+        <v>83</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>83</v>
@@ -9034,18 +9204,18 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>478</v>
+        <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>479</v>
+        <v>261</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -9069,13 +9239,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>83</v>
+        <v>265</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -9093,13 +9263,13 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
@@ -9114,7 +9284,7 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>482</v>
+        <v>267</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>165</v>
@@ -9123,7 +9293,7 @@
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9131,10 +9301,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9154,22 +9324,20 @@
         <v>83</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>439</v>
+        <v>496</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9218,7 +9386,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9227,7 +9395,7 @@
         <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>500</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>103</v>
@@ -9239,16 +9407,16 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>444</v>
+        <v>501</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>489</v>
+        <v>165</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>83</v>
+        <v>502</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
@@ -9256,10 +9424,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9270,32 +9438,28 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -9343,13 +9507,13 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>83</v>
@@ -9364,7 +9528,7 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>165</v>
@@ -9381,10 +9545,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9395,7 +9559,7 @@
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>83</v>
@@ -9407,16 +9571,20 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>262</v>
+        <v>325</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>263</v>
+        <v>508</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9464,19 +9632,19 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>265</v>
+        <v>507</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>83</v>
@@ -9485,10 +9653,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>165</v>
+        <v>512</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>83</v>
+        <v>513</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9502,21 +9670,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -9528,17 +9696,15 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9587,19 +9753,19 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>268</v>
+        <v>180</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
@@ -9625,14 +9791,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9645,26 +9811,24 @@
         <v>83</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>271</v>
+        <v>138</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>272</v>
+        <v>182</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O63" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
@@ -9712,7 +9876,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>273</v>
+        <v>186</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9733,7 +9897,7 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>83</v>
@@ -9750,44 +9914,46 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>83</v>
+        <v>335</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>500</v>
+        <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>501</v>
+        <v>336</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>502</v>
+        <v>337</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -9835,19 +10001,19 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>499</v>
+        <v>338</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>83</v>
@@ -9856,16 +10022,16 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>504</v>
+        <v>83</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -9873,10 +10039,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9896,19 +10062,23 @@
         <v>83</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
@@ -9932,13 +10102,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>193</v>
+        <v>115</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>507</v>
+        <v>116</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>508</v>
+        <v>117</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -9956,7 +10126,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -9977,23 +10147,1134 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="AN65" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AO65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ65">
+  <autoFilter ref="A1:AQ74">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10003,7 +11284,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalPatient.xlsx
+++ b/docs/StructureDefinition-DebtPortalPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -655,10 +655,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpp-17-1827:If POINTER is PATIENT (#2) then source value from (430-9 &gt; 340-.01) {true}</t>
-  </si>
-  <si>
-    <t>1827: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - DEBTOR (430-9 &gt; 340-.01) if POINTER is PATIENT (#2)</t>
+dpp-17-1827:If type is PATIENT (#2) then source value from (430-9 &gt; 340-.01) {true}</t>
+  </si>
+  <si>
+    <t>1827: source value based on ACCOUNTS RECEIVABLE - DEBTOR &gt; AR DEBTOR - DEBTOR (430-9 &gt; 340-.01) if type is PATIENT (#2)</t>
   </si>
   <si>
     <t>IB.AccountsReceivable.ARDebtorIEN
@@ -691,10 +691,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpp-17-1827-1:If POINTER is PATIENT (#2) then fixed value LAST {true}</t>
-  </si>
-  <si>
-    <t>1827-1: fixed value = LAST if POINTER is PATIENT (#2)</t>
+dpp-17-1827-1:If type is PATIENT (#2) then fixed value LAST {true}</t>
+  </si>
+  <si>
+    <t>1827-1: fixed value = LAST if type is PATIENT (#2)</t>
   </si>
   <si>
     <t>./part[partType = FAM]</t>
@@ -723,10 +723,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpp-17-1827-2:If POINTER is PATIENT (#2) then fixed value FIRST &amp; MIDDLE {true}</t>
-  </si>
-  <si>
-    <t>1827-2: fixed value = FIRST &amp; MIDDLE if POINTER is PATIENT (#2)</t>
+dpp-17-1827-2:If type is PATIENT (#2) then fixed value FIRST &amp; MIDDLE {true}</t>
+  </si>
+  <si>
+    <t>1827-2: fixed value = FIRST &amp; MIDDLE if type is PATIENT (#2)</t>
   </si>
   <si>
     <t>./part[partType = GIV]</t>
@@ -766,10 +766,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-dpp-17-1827-3:If POINTER is PATIENT (#2) then fixed value SUFFIX {true}</t>
-  </si>
-  <si>
-    <t>1827-3: fixed value = SUFFIX if POINTER is PATIENT (#2)</t>
+dpp-17-1827-3:If type is PATIENT (#2) then fixed value SUFFIX {true}</t>
+  </si>
+  <si>
+    <t>1827-3: fixed value = SUFFIX if type is PATIENT (#2)</t>
   </si>
   <si>
     <t>./part[partType = SFX]</t>
@@ -2136,7 +2136,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="125.31640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="121.3984375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="131.55859375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="40.8125" customWidth="true" bestFit="true"/>
